--- a/docs/build/lakeshore-enterprise-context/source/04_finance_performance/cash_working_capital.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/04_finance_performance/cash_working_capital.xlsx
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>766.1</v>
+        <v>510.4</v>
       </c>
       <c r="C3" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>320.8</v>
+        <v>155.8</v>
       </c>
       <c r="C4" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" t="n">
         <v>56</v>
-      </c>
-      <c r="E4" t="n">
-        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -522,16 +522,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>380.4</v>
+        <v>592.8</v>
       </c>
       <c r="C5" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -541,16 +541,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>152</v>
+        <v>754.9</v>
       </c>
       <c r="C6" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>592.6</v>
+        <v>103.1</v>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -579,16 +579,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>480.9</v>
+        <v>519.9</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.9</v>
+        <v>766.1</v>
       </c>
       <c r="C9" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -617,16 +617,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>880.3</v>
+        <v>320.8</v>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -636,16 +636,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.8</v>
+        <v>380.4</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>690.3</v>
+        <v>152</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
